--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.66730509850441</v>
+        <v>5.470937078506966</v>
       </c>
       <c r="D2" t="n">
-        <v>33.92146552080342</v>
+        <v>5.512238147130556</v>
       </c>
       <c r="E2" t="n">
-        <v>8.421347395091287</v>
+        <v>1.368468951702334</v>
       </c>
       <c r="F2" t="n">
-        <v>8.635242741860427</v>
+        <v>1.403226945552319</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.91095929474456</v>
+        <v>4.048030885395991</v>
       </c>
       <c r="D3" t="n">
-        <v>25.52943520566447</v>
+        <v>4.148533220920476</v>
       </c>
       <c r="E3" t="n">
-        <v>8.421347395091287</v>
+        <v>1.368468951702334</v>
       </c>
       <c r="F3" t="n">
-        <v>8.635242741860427</v>
+        <v>1.403226945552319</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.552235622669551</v>
+        <v>1.552238288683802</v>
       </c>
       <c r="D4" t="n">
-        <v>9.218715370963855</v>
+        <v>1.498041247781627</v>
       </c>
       <c r="E4" t="n">
-        <v>8.421347395091287</v>
+        <v>1.368468951702334</v>
       </c>
       <c r="F4" t="n">
-        <v>8.635242741860427</v>
+        <v>1.403226945552319</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.7628275921227</v>
+        <v>2.398959483719938</v>
       </c>
       <c r="D5" t="n">
-        <v>14.66545165759686</v>
+        <v>2.38313589435949</v>
       </c>
       <c r="E5" t="n">
-        <v>8.421347395091287</v>
+        <v>1.368468951702334</v>
       </c>
       <c r="F5" t="n">
-        <v>8.635242741860427</v>
+        <v>1.403226945552319</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.35560727104506</v>
+        <v>2.820286181544822</v>
       </c>
       <c r="D6" t="n">
-        <v>19.14778672597287</v>
+        <v>3.111515342970591</v>
       </c>
       <c r="E6" t="n">
-        <v>8.421347395091287</v>
+        <v>1.368468951702334</v>
       </c>
       <c r="F6" t="n">
-        <v>8.635242741860427</v>
+        <v>1.403226945552319</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.81695681350422</v>
+        <v>1.757755482194435</v>
       </c>
       <c r="D7" t="n">
-        <v>10.77016628616049</v>
+        <v>1.750152021501079</v>
       </c>
       <c r="E7" t="n">
-        <v>8.421347395091287</v>
+        <v>1.368468951702334</v>
       </c>
       <c r="F7" t="n">
-        <v>8.635242741860427</v>
+        <v>1.403226945552319</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
